--- a/dataset/GroundTruth/DataGroundTruth.xlsx
+++ b/dataset/GroundTruth/DataGroundTruth.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lakshmi_Barthwal\Desktop\MtechNUS-AIS\practiseModuleProject\21AprilRecommenderSystem\IRS-MR-CV-Recommender-System\dataset\GroundTruth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB8A9D-599C-4A86-AF2F-ACC5D3BA7B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8FD34F-58E4-4084-8517-7868A6004F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1416" yWindow="1020" windowWidth="21624" windowHeight="11220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21624" windowHeight="11220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GroundTruthScores" sheetId="1" r:id="rId1"/>
     <sheet name="Methodology" sheetId="2" r:id="rId2"/>
+    <sheet name="JDnCVGroundTruth" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="345">
   <si>
     <t>1. skills_score</t>
   </si>
@@ -64,9 +65,6 @@
     <t>11.Overqualification_flag(Penality)</t>
   </si>
   <si>
-    <t>9. education_gap_flag(Penality)</t>
-  </si>
-  <si>
     <t>12. Career_stability_concerns_flag(Penality)</t>
   </si>
   <si>
@@ -124,14 +122,1384 @@
     <t>JD_ID</t>
   </si>
   <si>
-    <t>Resume_ID</t>
+    <t>1. Eligibility label</t>
+  </si>
+  <si>
+    <r>
+      <t>Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD0D0D0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Eligible / Not Eligible</t>
+    </r>
+  </si>
+  <si>
+    <t>Reason: the current pipeline first filters candidates before ranking them. A candidate may have some good scores but still be marked not applicable.</t>
+  </si>
+  <si>
+    <t>2. Availability or notice period</t>
+  </si>
+  <si>
+    <t>Reason: this is one of the 5 actual ranking dimensions in scoring_engine.py:233. If your ground truth ignores it, your labels will not match the model.</t>
+  </si>
+  <si>
+    <t>3. Final human rank per JD</t>
+  </si>
+  <si>
+    <r>
+      <t>Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD0D0D0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Rank 1, Rank 2, Rank 3...</t>
+    </r>
+  </si>
+  <si>
+    <t>Reason: the GA optimizer in ga_optimizer.py:136 ultimately needs expected ranking order, not only isolated dimension scores.</t>
+  </si>
+  <si>
+    <t>4. Overall suitability score</t>
+  </si>
+  <si>
+    <r>
+      <t>Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD0D0D0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0-100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD0D0D0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1-5</t>
+    </r>
+  </si>
+  <si>
+    <t>Reason: useful for tie-breaking and quality checks between candidates with similar ranks.</t>
+  </si>
+  <si>
+    <t>5. Reason or evidence column</t>
+  </si>
+  <si>
+    <t>Example: brief justification for each score</t>
+  </si>
+  <si>
+    <t>Reason: otherwise the LLM may generate inconsistent labels and you cannot audit them later.</t>
+  </si>
+  <si>
+    <t>6. Separate flags instead of burying everything inside misc</t>
+  </si>
+  <si>
+    <t>Reason: your code has bonus and penalty conditions in expert_flags.py. Those should be explicit columns if they matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to use LLM for collecting ground truth </t>
+  </si>
+  <si>
+    <t>current system</t>
+  </si>
+  <si>
+    <t>Candidate_ID</t>
+  </si>
+  <si>
+    <t>9. upskill_flag(Bonus)</t>
+  </si>
+  <si>
+    <t>1. Ground Truth Schema (Final Format)</t>
+  </si>
+  <si>
+    <t>JD_ID,</t>
+  </si>
+  <si>
+    <t>Candidate_ID,</t>
+  </si>
+  <si>
+    <t>Eligible,</t>
+  </si>
+  <si>
+    <t>Eligibility_reason,</t>
+  </si>
+  <si>
+    <t>Final_Rank_Per_JD,</t>
+  </si>
+  <si>
+    <t>skills_score,</t>
+  </si>
+  <si>
+    <t>experience_score,</t>
+  </si>
+  <si>
+    <t>education_score,</t>
+  </si>
+  <si>
+    <t>availability_score,</t>
+  </si>
+  <si>
+    <t>misc_score,</t>
+  </si>
+  <si>
+    <t>relocation_flag,</t>
+  </si>
+  <si>
+    <t>work_visa_flag,</t>
+  </si>
+  <si>
+    <t>career_gap_flag,</t>
+  </si>
+  <si>
+    <t>education_gap_flag,</t>
+  </si>
+  <si>
+    <t>certification_score,</t>
+  </si>
+  <si>
+    <t>overqualification_flag,</t>
+  </si>
+  <si>
+    <t>career_stability_flag,</t>
+  </si>
+  <si>
+    <t>LLM_Justification</t>
+  </si>
+  <si>
+    <t>✅ 2. Scoring Framework (Out of 100 Each)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You MUST normalize every dimension to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0–100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, otherwise GA optimization will be biased.</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 1. Skills Score (0–100)</t>
+  </si>
+  <si>
+    <t>Assumption:</t>
+  </si>
+  <si>
+    <t>Extract JD required skills (NER / keyword / ontology)</t>
+  </si>
+  <si>
+    <t>Match with CV skills (exact + semantic match via BERT)</t>
+  </si>
+  <si>
+    <t>Formula:</t>
+  </si>
+  <si>
+    <t>skills_score = (matched_skills / total_required_skills) * 100</t>
+  </si>
+  <si>
+    <t>Enhancement:</t>
+  </si>
+  <si>
+    <t>Core skills weight = 70%</t>
+  </si>
+  <si>
+    <t>Secondary skills weight = 30%</t>
+  </si>
+  <si>
+    <t>🔹 2. Experience Score (0–100)</t>
+  </si>
+  <si>
+    <t>JD Requirement Example:</t>
+  </si>
+  <si>
+    <t>Required: 5 years</t>
+  </si>
+  <si>
+    <t>Logic:</t>
+  </si>
+  <si>
+    <t>Candidate Experience</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>&lt; 50% of required</t>
+  </si>
+  <si>
+    <t>50–100%</t>
+  </si>
+  <si>
+    <t>linear (50–100)</t>
+  </si>
+  <si>
+    <t>100–150%</t>
+  </si>
+  <si>
+    <t>&gt;150%</t>
+  </si>
+  <si>
+    <t>90 (penalty for overqualification handled separately)</t>
+  </si>
+  <si>
+    <t>🔹 3. Education Score (0–100)</t>
+  </si>
+  <si>
+    <t>Mapping:</t>
+  </si>
+  <si>
+    <t>JD Requirement</t>
+  </si>
+  <si>
+    <t>Candidate</t>
+  </si>
+  <si>
+    <t>Exact match</t>
+  </si>
+  <si>
+    <t>Same</t>
+  </si>
+  <si>
+    <t>Higher</t>
+  </si>
+  <si>
+    <t>Better</t>
+  </si>
+  <si>
+    <t>Related field</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Unrelated</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>🔹 4. Availability Score (0–100)</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>Immediate</t>
+  </si>
+  <si>
+    <t>&lt; 30 days</t>
+  </si>
+  <si>
+    <t>1–3 months</t>
+  </si>
+  <si>
+    <t>&gt;3 months</t>
+  </si>
+  <si>
+    <t>🔹 5. Misc Score (0–100)</t>
+  </si>
+  <si>
+    <t>Includes:</t>
+  </si>
+  <si>
+    <t>Title relevance</t>
+  </si>
+  <si>
+    <t>Domain fit</t>
+  </si>
+  <si>
+    <t>Company relevance</t>
+  </si>
+  <si>
+    <t>Example:</t>
+  </si>
+  <si>
+    <t>misc_score = (title_match * 0.5 + domain_match * 0.3 + company_fit * 0.2) * 100</t>
+  </si>
+  <si>
+    <t>🔹 6. Certification Score (0–100)</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Relevant certifications</t>
+  </si>
+  <si>
+    <t>90–100</t>
+  </si>
+  <si>
+    <t>Some certifications</t>
+  </si>
+  <si>
+    <t>60–80</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>20–40</t>
+  </si>
+  <si>
+    <t>🚩 3. Flags Logic (Binary but impacts reasoning)</t>
+  </si>
+  <si>
+    <t>🔸 6. Relocation Flag</t>
+  </si>
+  <si>
+    <t>TRUE → candidate needs relocation → penalty</t>
+  </si>
+  <si>
+    <t>FALSE → already in location</t>
+  </si>
+  <si>
+    <t>🔸 7. Work Visa Flag</t>
+  </si>
+  <si>
+    <t>TRUE → visa available → bonus</t>
+  </si>
+  <si>
+    <t>FALSE → penalty (critical in SG/US hiring)</t>
+  </si>
+  <si>
+    <t>🔸 8. Career Gap Flag</t>
+  </si>
+  <si>
+    <t>Gap &gt; 1 year → TRUE</t>
+  </si>
+  <si>
+    <t>🔸 9. Education Gap Flag</t>
+  </si>
+  <si>
+    <t>Irregular academic progression → TRUE</t>
+  </si>
+  <si>
+    <t>🔸 10. Overqualification Flag</t>
+  </si>
+  <si>
+    <t>Candidate experience &gt; 150% of JD</t>
+  </si>
+  <si>
+    <t>🔸 11. Career Stability Flag</t>
+  </si>
+  <si>
+    <t>5 job switches in 10 years → TRUE</t>
+  </si>
+  <si>
+    <t>🧠 4. Eligibility Logic (CRITICAL)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>top 5 candidates per JD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should be marked:</t>
+    </r>
+  </si>
+  <si>
+    <t>Eligible = YES (only for top 5)</t>
+  </si>
+  <si>
+    <t>Else = NO</t>
+  </si>
+  <si>
+    <t>Eligibility Criteria:</t>
+  </si>
+  <si>
+    <t>Weighted composite score:</t>
+  </si>
+  <si>
+    <t>Final Score =</t>
+  </si>
+  <si>
+    <t>0.30 * skills +</t>
+  </si>
+  <si>
+    <t>0.20 * experience +</t>
+  </si>
+  <si>
+    <t>0.15 * education +</t>
+  </si>
+  <si>
+    <t>0.10 * availability +</t>
+  </si>
+  <si>
+    <t>0.15 * misc +</t>
+  </si>
+  <si>
+    <t>0.10 * certification</t>
+  </si>
+  <si>
+    <t>Apply penalties:</t>
+  </si>
+  <si>
+    <t>Work visa missing → -20</t>
+  </si>
+  <si>
+    <t>Relocation needed → -10</t>
+  </si>
+  <si>
+    <t>Career gap → -10</t>
+  </si>
+  <si>
+    <t>Stability → -10</t>
+  </si>
+  <si>
+    <t>🏆 5. Ranking Logic</t>
+  </si>
+  <si>
+    <t>For each JD:</t>
+  </si>
+  <si>
+    <t>1. Compute final score</t>
+  </si>
+  <si>
+    <t>2. Sort descending</t>
+  </si>
+  <si>
+    <t>3. Pick top 5 → Eligible = YES</t>
+  </si>
+  <si>
+    <t>4. Assign ranks 1–5</t>
+  </si>
+  <si>
+    <t>🧾 6. LLM Justification Structure</t>
+  </si>
+  <si>
+    <t>You must make this structured (VERY IMPORTANT for explainability):</t>
+  </si>
+  <si>
+    <t>Template:</t>
+  </si>
+  <si>
+    <t>Candidate selected as top 5 due to strong alignment with JD.</t>
+  </si>
+  <si>
+    <t>Skills: Matched X/Y required skills including [A, B, C], resulting in score of XX.</t>
+  </si>
+  <si>
+    <t>Experience: Candidate has X years vs required Y years, giving score XX.</t>
+  </si>
+  <si>
+    <t>Education: Degree in [field], aligned with JD requirement, score XX.</t>
+  </si>
+  <si>
+    <t>Availability: Available in X days, score XX.</t>
+  </si>
+  <si>
+    <t>Misc: Previous role as [title] in [domain], strong relevance.</t>
+  </si>
+  <si>
+    <t>Flags:</t>
+  </si>
+  <si>
+    <t>- Relocation: TRUE → Candidate not in job location.</t>
+  </si>
+  <si>
+    <t>- Work Visa: FALSE → No valid work authorization.</t>
+  </si>
+  <si>
+    <t>- Career Gap: TRUE → Gap of X months observed.</t>
+  </si>
+  <si>
+    <t>- Overqualification: FALSE → Experience within acceptable range.</t>
+  </si>
+  <si>
+    <t>- Career Stability: TRUE → Frequent job changes observed.</t>
+  </si>
+  <si>
+    <t>Final decision: Ranked #X due to overall score of XX.</t>
+  </si>
+  <si>
+    <t>📊 7. Sample Ground Truth Rows</t>
+  </si>
+  <si>
+    <t>JD_001,CD_0001,YES,Strong skill and experience match,1,</t>
+  </si>
+  <si>
+    <t>92,95,90,85,88,</t>
+  </si>
+  <si>
+    <t>FALSE,TRUE,FALSE,FALSE,</t>
+  </si>
+  <si>
+    <t>85,FALSE,FALSE,</t>
+  </si>
+  <si>
+    <t>"Candidate selected as top 5 due to strong alignment...</t>
+  </si>
+  <si>
+    <t>Skills: 8/9 matched...</t>
+  </si>
+  <si>
+    <t>Experience: 10 yrs vs 8 yrs...</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>Final Rank: 1"</t>
+  </si>
+  <si>
+    <t>JD_001,CD_0002,YES,Good match but relocation needed,2,</t>
+  </si>
+  <si>
+    <t>85,88,85,70,80,</t>
+  </si>
+  <si>
+    <t>TRUE,TRUE,FALSE,FALSE,</t>
+  </si>
+  <si>
+    <t>75,FALSE,TRUE,</t>
+  </si>
+  <si>
+    <t>"Candidate selected due to strong technical skills...</t>
+  </si>
+  <si>
+    <t>Relocation required causing minor penalty..."</t>
+  </si>
+  <si>
+    <t>JD_001,CD_0008,NO,Low skill match,NA,</t>
+  </si>
+  <si>
+    <t>40,60,70,90,50,</t>
+  </si>
+  <si>
+    <t>40,FALSE,FALSE,</t>
+  </si>
+  <si>
+    <t>"Candidate not selected due to insufficient skill alignment..."</t>
+  </si>
+  <si>
+    <t>⚠️ 8. Critical Observations (From Industry Systems)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ground truth must be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>human-auditable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Scores must be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>explainable (not black box)</t>
+    </r>
+  </si>
+  <si>
+    <t>Flags should NOT directly zero out candidates (only penalize)</t>
+  </si>
+  <si>
+    <t>LLM justification should NOT contradict numeric scores</t>
+  </si>
+  <si>
+    <t>or 4 job switch in 5 years -&gt; TRUE</t>
+  </si>
+  <si>
+    <t>CD_S0001</t>
+  </si>
+  <si>
+    <t>JD_001</t>
+  </si>
+  <si>
+    <t>YES,Strong ML + backend + distributed exposure,1,</t>
+  </si>
+  <si>
+    <t>92,90,88,85,90,</t>
+  </si>
+  <si>
+    <t>"Selected as top candidate due to strong alignment.</t>
+  </si>
+  <si>
+    <t>Skills: Extensive Python, ML, NLP, ElasticSearch, Kafka, Docker → 92</t>
+  </si>
+  <si>
+    <t>Experience: ~2–3 yrs relevant but strong project depth → 90</t>
+  </si>
+  <si>
+    <t>Education: Data science aligned → 88</t>
+  </si>
+  <si>
+    <t>Availability: assumed standard → 85</t>
+  </si>
+  <si>
+    <t>Misc: strong domain (fraud analytics, large-scale systems) → 90</t>
+  </si>
+  <si>
+    <t>Ground truth reflects real-world hiring complexity:</t>
+  </si>
+  <si>
+    <t>- Mix of overqualified leadership candidates</t>
+  </si>
+  <si>
+    <t>- Platform vs backend trade-offs</t>
+  </si>
+  <si>
+    <t>- CI/CD and developer productivity as primary signals</t>
+  </si>
+  <si>
+    <t>Dataset ranking</t>
+  </si>
+  <si>
+    <t>"The ranking system dynamically adapts feature weights based on JD intent:</t>
+  </si>
+  <si>
+    <t>- Technical roles prioritize skills and experience</t>
+  </si>
+  <si>
+    <t>- Entry-level roles prioritize communication, adaptability, and customer exposure</t>
+  </si>
+  <si>
+    <t>- Overqualification is treated as a penalty in junior roles"</t>
+  </si>
+  <si>
+    <t>JD_006</t>
+  </si>
+  <si>
+    <t>Weighting Logic (Adjusted for this JD)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Communication / customer-facing → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>35%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adaptability / learning → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experience (only relevant if customer-facing) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Education → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Misc (energy, leadership exposure) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20%</t>
+    </r>
+  </si>
+  <si>
+    <t>enalties:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Overqualification → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Purely technical (no people exposure) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-10</t>
+    </r>
+  </si>
+  <si>
+    <t>System dynamically adjusts ranking strategy based on job intent:</t>
+  </si>
+  <si>
+    <t>- Technical roles prioritize skills &amp; systems experience</t>
+  </si>
+  <si>
+    <t>- Leadership roles prioritize architecture &amp; scale</t>
+  </si>
+  <si>
+    <t>- Entry-level roles prioritize communication &amp; adaptability</t>
+  </si>
+  <si>
+    <t>Overqualification is penalized differently depending on JD type.</t>
+  </si>
+  <si>
+    <t>JD_007</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Communication / people skills → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>40%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adaptability / attitude → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Customer exposure → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Misc (energy, team fit) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20%</t>
+    </r>
+  </si>
+  <si>
+    <t>Penalty:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Overqualification → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Highly technical (low people exposure) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-15</t>
+    </r>
+  </si>
+  <si>
+    <t>Overqualified / Misfit</t>
+  </si>
+  <si>
+    <t>CD_007_KL (CTO) → ❌ Too senior (high penalty)</t>
+  </si>
+  <si>
+    <t>CD_009_LBC → ❌ Leadership mismatch</t>
+  </si>
+  <si>
+    <t>CD_011_TB → ❌ Architect (low people-facing)</t>
+  </si>
+  <si>
+    <t>CD_013_ARB → ❌ Systems engineer (low communication exposure)</t>
+  </si>
+  <si>
+    <t>JD_009 – Sales Director (P&amp;G, APAC Strategy)</t>
+  </si>
+  <si>
+    <t>JD_011 – Cafe Service Crew</t>
+  </si>
+  <si>
+    <t>What matters:</t>
+  </si>
+  <si>
+    <t>Leadership (very high)</t>
+  </si>
+  <si>
+    <t>FMCG / strategy / GTM</t>
+  </si>
+  <si>
+    <t>Stakeholder influence</t>
+  </si>
+  <si>
+    <t>Regional exposure</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">our dataset has </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NO pure FMCG Sales Directors</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 So ranking = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>closest transferable leadership + strategy profiles</t>
+    </r>
+  </si>
+  <si>
+    <t>Customer service</t>
+  </si>
+  <si>
+    <t>Fast-paced environment</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>Reliability</t>
+  </si>
+  <si>
+    <t>JD_012 – Chef Role</t>
+  </si>
+  <si>
+    <t>Cooking experience</t>
+  </si>
+  <si>
+    <t>Kitchen operations</t>
+  </si>
+  <si>
+    <t>Hygiene &amp; compliance</t>
+  </si>
+  <si>
+    <t>Food preparation skills</t>
+  </si>
+  <si>
+    <t>JD_003 – Principal Engineer (Singapore Govt, 10+ yrs leadership)</t>
+  </si>
+  <si>
+    <t>10+ yrs experience</t>
+  </si>
+  <si>
+    <t>DevOps + cloud-native</t>
+  </si>
+  <si>
+    <t>Architecture ownership</t>
+  </si>
+  <si>
+    <t>Team leadership</t>
+  </si>
+  <si>
+    <t>JD_004 – Technical Lead (Banking / Fintech)</t>
+  </si>
+  <si>
+    <t>Core Signals:</t>
+  </si>
+  <si>
+    <t>Banking domain</t>
+  </si>
+  <si>
+    <t>Transaction systems</t>
+  </si>
+  <si>
+    <t>Backend + DB mastery</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>JD_005 – ML Dev Enablement (Agentic AI + Infra)</t>
+  </si>
+  <si>
+    <t>Python / ML / LLM</t>
+  </si>
+  <si>
+    <t>Infra (Kubernetes, AWS)</t>
+  </si>
+  <si>
+    <t>Dev platform / tooling</t>
+  </si>
+  <si>
+    <t>Penalties:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">JD_006 is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>entry-level sales/marketing</t>
+    </r>
+  </si>
+  <si>
+    <t>IMPORTANT REJECTIONS (NOT IN TOP 10)</t>
+  </si>
+  <si>
+    <t>🚫 Overqualified Leadership Profiles</t>
+  </si>
+  <si>
+    <t>CD_007_KL (CTO) → ❌ Too senior</t>
+  </si>
+  <si>
+    <t>CD_009_LBC → ❌ Architect level</t>
+  </si>
+  <si>
+    <t>CD_011_TB → ❌ Infra architect</t>
+  </si>
+  <si>
+    <t>CD_013_ARB → ❌ Systems engineer</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 These were </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>correctly penalized</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> due to:</t>
+    </r>
+  </si>
+  <si>
+    <t>Misalignment with entry-level role</t>
+  </si>
+  <si>
+    <t>Risk of attrition</t>
+  </si>
+  <si>
+    <t>Dynamic Ranking Behavior</t>
+  </si>
+  <si>
+    <t>JD Type</t>
+  </si>
+  <si>
+    <t>Top Candidates</t>
+  </si>
+  <si>
+    <t>Technical (JD_001)</t>
+  </si>
+  <si>
+    <t>Engineers</t>
+  </si>
+  <si>
+    <t>Platform (JD_002)</t>
+  </si>
+  <si>
+    <t>Architects / CTO</t>
+  </si>
+  <si>
+    <t>Entry-level Sales (JD_006)</t>
+  </si>
+  <si>
+    <t>Customer-facing / junior</t>
+  </si>
+  <si>
+    <t>Key Adjustment vs JD_006</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>Personality / Energy</t>
+  </si>
+  <si>
+    <t>Overqualification penalty</t>
+  </si>
+  <si>
+    <t>“Fun Team Hiring – Sales &amp; Marketing”</t>
+  </si>
+  <si>
+    <t>JD_036 – Party Host</t>
+  </si>
+  <si>
+    <t>High Weight:</t>
+  </si>
+  <si>
+    <t>Communication &amp; energy</t>
+  </si>
+  <si>
+    <t>Customer interaction (kids + parents)</t>
+  </si>
+  <si>
+    <t>Hospitality / retail exposure</t>
+  </si>
+  <si>
+    <t>Enthusiasm / personality</t>
+  </si>
+  <si>
+    <t>⚠️ Medium:</t>
+  </si>
+  <si>
+    <t>Adaptability / learning</t>
+  </si>
+  <si>
+    <t>❌ Low:</t>
+  </si>
+  <si>
+    <t>Technical skills</t>
+  </si>
+  <si>
+    <t>Deep experience</t>
+  </si>
+  <si>
+    <t>🚫 Strong Penalty:</t>
+  </si>
+  <si>
+    <t>Overqualification (CTO / Architect types)</t>
+  </si>
+  <si>
+    <t>Weight Model (Used for scoring)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Communication / personality → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>40%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Customer-facing experience → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adaptability → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Energy / team fit → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No people interaction → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-15</t>
+    </r>
+  </si>
+  <si>
+    <t>NON-ELIGIBLE (Important for Ground Truth)</t>
+  </si>
+  <si>
+    <t>🚫 Rejected Profiles:</t>
+  </si>
+  <si>
+    <t>CD_007_KL (CTO)</t>
+  </si>
+  <si>
+    <t>CD_009_LBC (Architect)</t>
+  </si>
+  <si>
+    <t>CD_011_TB (Solution Architect)</t>
+  </si>
+  <si>
+    <t>CD_013_ARB (Systems Engineer)</t>
+  </si>
+  <si>
+    <t>Same dataset → Completely different ranking → Based on job intent</t>
+  </si>
+  <si>
+    <t>Your system is:</t>
+  </si>
+  <si>
+    <t>✅ Context-aware</t>
+  </si>
+  <si>
+    <t>✅ Role-sensitive</t>
+  </si>
+  <si>
+    <t>✅ Explainable</t>
+  </si>
+  <si>
+    <t>✅ Real-world aligned</t>
+  </si>
+  <si>
+    <t>GA optimized</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +1529,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFD0D0D0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -185,17 +1602,57 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -474,8 +1931,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="16.21875" customWidth="1"/>
     <col min="3" max="4" width="23.88671875" customWidth="1"/>
@@ -493,24 +1950,24 @@
     <col min="19" max="19" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:19">
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
+      <c r="D1" t="s">
+        <v>25</v>
       </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -528,16 +1985,16 @@
         <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
-        <v>25</v>
-      </c>
       <c r="O1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="P1" t="s">
         <v>5</v>
@@ -546,10 +2003,66 @@
         <v>7</v>
       </c>
       <c r="R1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S1" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="C3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="C4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="C5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="C6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="C8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="C9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="C10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="C11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="C12" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -559,60 +2072,1726 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA48E86F-0992-4C62-A6D3-C5B52AF07C7D}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I259"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="47.6640625" customWidth="1"/>
+    <col min="7" max="7" width="73.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:7" ht="31.2">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+      <c r="G7" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="G9" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="G13" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="34.200000000000003">
+      <c r="A17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4"/>
+      <c r="G18" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.2">
+      <c r="A20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4"/>
+      <c r="G21" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.2">
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4"/>
+      <c r="G25" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="22.8">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:7" ht="31.2">
+      <c r="A30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="22.8">
+      <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="43.2">
+      <c r="A35" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="23.4">
+      <c r="G36" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18">
+      <c r="G38" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="G40" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="G41" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="18">
+      <c r="G43" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="G45" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="18">
+      <c r="G47" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="7:8">
+      <c r="G49" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8">
+      <c r="G50" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" ht="23.4">
+      <c r="G54" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8" ht="18">
+      <c r="G56" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8">
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="7:8">
+      <c r="G58" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8" ht="18">
+      <c r="G60" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8" ht="57.6">
+      <c r="G62" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8" ht="28.8">
+      <c r="G63" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H63" s="14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8" ht="28.8">
+      <c r="G64" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="7:9" ht="28.8">
+      <c r="G65" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H65" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="7:9" ht="115.2">
+      <c r="G66" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="7:9" ht="23.4">
+      <c r="G69" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="7:9" ht="18">
+      <c r="G71" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="7:9" ht="43.2">
+      <c r="G73" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="7:9" ht="28.8">
+      <c r="G74" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I74" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="7:9">
+      <c r="G75" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I75" s="14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="7:9" ht="28.8">
+      <c r="G76" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="I76" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="7:9" ht="28.8">
+      <c r="G77" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="I77" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="7:9" ht="23.4">
+      <c r="G80" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="7:8" ht="28.8">
+      <c r="G82" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="7:8" ht="28.8">
+      <c r="G83" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H83" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="7:8">
+      <c r="G84" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="H84" s="14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="7:8" ht="28.8">
+      <c r="G85" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H85" s="14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="7:8" ht="28.8">
+      <c r="G86" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H86" s="14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="7:8" ht="23.4">
+      <c r="G89" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="7:8">
+      <c r="G91" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="7:8">
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="7:8">
+      <c r="G93" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="7:8">
+      <c r="G94" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="7:8">
+      <c r="G95" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="97" spans="7:8" ht="18">
+      <c r="G97" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="98" spans="7:8">
+      <c r="G98" s="7"/>
+    </row>
+    <row r="99" spans="7:8">
+      <c r="G99" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="7:8" ht="23.4">
+      <c r="G103" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="105" spans="7:8" ht="28.8">
+      <c r="G105" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="7:8" ht="43.2">
+      <c r="G106" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="107" spans="7:8" ht="43.2">
+      <c r="G107" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="108" spans="7:8">
+      <c r="G108" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H108" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="111" spans="7:8" ht="31.2">
+      <c r="G111" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="7:7" ht="23.4">
+      <c r="G115" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="7:7">
+      <c r="G116" s="12"/>
+    </row>
+    <row r="117" spans="7:7">
+      <c r="G117" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="118" spans="7:7">
+      <c r="G118" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="122" spans="7:7" ht="23.4">
+      <c r="G122" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="7:7">
+      <c r="G123" s="12"/>
+    </row>
+    <row r="124" spans="7:7">
+      <c r="G124" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="125" spans="7:7">
+      <c r="G125" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="7:7" ht="23.4">
+      <c r="G129" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="7:7">
+      <c r="G130" s="12"/>
+    </row>
+    <row r="131" spans="7:7">
+      <c r="G131" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="7:7" ht="23.4">
+      <c r="G135" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="7:7">
+      <c r="G136" s="12"/>
+    </row>
+    <row r="137" spans="7:7">
+      <c r="G137" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="141" spans="7:7" ht="23.4">
+      <c r="G141" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="142" spans="7:7">
+      <c r="G142" s="12"/>
+    </row>
+    <row r="143" spans="7:7">
+      <c r="G143" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="147" spans="7:7" ht="23.4">
+      <c r="G147" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="148" spans="7:7">
+      <c r="G148" s="15"/>
+    </row>
+    <row r="149" spans="7:7">
+      <c r="G149" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="150" spans="7:7">
+      <c r="G150" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="153" spans="7:7" ht="31.2">
+      <c r="G153" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="155" spans="7:7">
+      <c r="G155" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="156" spans="7:7">
+      <c r="G156" s="7"/>
+    </row>
+    <row r="157" spans="7:7">
+      <c r="G157" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="7:7">
+      <c r="G158" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="162" spans="7:8" ht="18">
+      <c r="G162" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H162" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="164" spans="7:8">
+      <c r="G164" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="165" spans="7:8">
+      <c r="G165" s="7"/>
+    </row>
+    <row r="166" spans="7:8">
+      <c r="G166" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="167" spans="7:8">
+      <c r="G167" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="168" spans="7:8">
+      <c r="G168" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="169" spans="7:8">
+      <c r="G169" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="170" spans="7:8">
+      <c r="G170" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="171" spans="7:8">
+      <c r="G171" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="172" spans="7:8">
+      <c r="G172" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="174" spans="7:8">
+      <c r="G174" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="175" spans="7:8">
+      <c r="G175" s="12"/>
+    </row>
+    <row r="176" spans="7:8">
+      <c r="G176" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="177" spans="7:7">
+      <c r="G177" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="178" spans="7:7">
+      <c r="G178" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="179" spans="7:7">
+      <c r="G179" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="183" spans="7:7" ht="31.2">
+      <c r="G183" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="185" spans="7:7">
+      <c r="G185" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="186" spans="7:7">
+      <c r="G186" s="12"/>
+    </row>
+    <row r="187" spans="7:7">
+      <c r="G187" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="188" spans="7:7">
+      <c r="G188" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="189" spans="7:7">
+      <c r="G189" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="190" spans="7:7">
+      <c r="G190" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="194" spans="7:7" ht="31.2">
+      <c r="G194" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="196" spans="7:7">
+      <c r="G196" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="200" spans="7:7" ht="18">
+      <c r="G200" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="201" spans="7:7">
+      <c r="G201" s="7"/>
+    </row>
+    <row r="202" spans="7:7">
+      <c r="G202" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="203" spans="7:7">
+      <c r="G203" s="7"/>
+    </row>
+    <row r="204" spans="7:7">
+      <c r="G204" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="205" spans="7:7">
+      <c r="G205" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="206" spans="7:7">
+      <c r="G206" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="207" spans="7:7">
+      <c r="G207" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="208" spans="7:7">
+      <c r="G208" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="209" spans="7:7">
+      <c r="G209" s="7"/>
+    </row>
+    <row r="210" spans="7:7">
+      <c r="G210" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="211" spans="7:7">
+      <c r="G211" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="212" spans="7:7">
+      <c r="G212" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="213" spans="7:7">
+      <c r="G213" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="214" spans="7:7">
+      <c r="G214" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="215" spans="7:7">
+      <c r="G215" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="216" spans="7:7">
+      <c r="G216" s="7"/>
+    </row>
+    <row r="217" spans="7:7">
+      <c r="G217" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="221" spans="7:7" ht="31.2">
+      <c r="G221" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="222" spans="7:7">
+      <c r="G222" s="7"/>
+    </row>
+    <row r="223" spans="7:7">
+      <c r="G223" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="224" spans="7:7">
+      <c r="G224" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="225" spans="7:7">
+      <c r="G225" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="226" spans="7:7">
+      <c r="G226" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="227" spans="7:7">
+      <c r="G227" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="228" spans="7:7">
+      <c r="G228" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="229" spans="7:7">
+      <c r="G229" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="230" spans="7:7">
+      <c r="G230" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="231" spans="7:7">
+      <c r="G231" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="232" spans="7:7">
+      <c r="G232" s="7"/>
+    </row>
+    <row r="233" spans="7:7">
+      <c r="G233" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="234" spans="7:7">
+      <c r="G234" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="235" spans="7:7">
+      <c r="G235" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="236" spans="7:7">
+      <c r="G236" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="237" spans="7:7">
+      <c r="G237" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="238" spans="7:7">
+      <c r="G238" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="239" spans="7:7">
+      <c r="G239" s="7"/>
+    </row>
+    <row r="240" spans="7:7">
+      <c r="G240" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="241" spans="7:7">
+      <c r="G241" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="242" spans="7:7">
+      <c r="G242" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="243" spans="7:7">
+      <c r="G243" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="244" spans="7:7">
+      <c r="G244" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="248" spans="7:7" ht="31.2">
+      <c r="G248" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="249" spans="7:7">
+      <c r="G249" s="12"/>
+    </row>
+    <row r="250" spans="7:7">
+      <c r="G250" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="251" spans="7:7">
+      <c r="G251" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="252" spans="7:7">
+      <c r="G252" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="253" spans="7:7">
+      <c r="G253" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="256" spans="7:7">
+      <c r="G256" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="257" spans="7:7">
+      <c r="G257" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="258" spans="7:7">
+      <c r="G258" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="259" spans="7:7">
+      <c r="G259" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A20" r:id="rId1" display="vscode-file://vscode-app/c:/Users/Lakshmi_Barthwal/AppData/Local/Programs/Microsoft VS Code/ce099c1ed2/resources/app/out/vs/code/electron-browser/workbench/workbench.html" xr:uid="{DBB91B62-F7E4-4CB9-A459-FE6554F0AA8D}"/>
+    <hyperlink ref="A24" r:id="rId2" display="vscode-file://vscode-app/c:/Users/Lakshmi_Barthwal/AppData/Local/Programs/Microsoft VS Code/ce099c1ed2/resources/app/out/vs/code/electron-browser/workbench/workbench.html" xr:uid="{9918E602-E303-4CE7-8AB6-C899138E1BD8}"/>
+    <hyperlink ref="A35" r:id="rId3" display="vscode-file://vscode-app/c:/Users/Lakshmi_Barthwal/AppData/Local/Programs/Microsoft VS Code/ce099c1ed2/resources/app/out/vs/code/electron-browser/workbench/workbench.html" xr:uid="{9F25BC3C-A94D-4991-B141-E53FC52394E3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C636A3C-9C39-4BC3-B7F3-EC460D188C18}">
+  <dimension ref="A1:T127"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="46.21875" customWidth="1"/>
+    <col min="16" max="16" width="41.44140625" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" customWidth="1"/>
+    <col min="20" max="20" width="15.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="18">
+      <c r="A3" t="s">
+        <v>218</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="43.2">
+      <c r="A5" t="s">
+        <v>220</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="28.8">
+      <c r="A6" t="s">
+        <v>221</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="28.8">
+      <c r="S7" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="57.6">
+      <c r="S8" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="18">
+      <c r="B10" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="B11" s="12"/>
+      <c r="H11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="B12" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="B13" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="B14" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="B15" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="31.2">
+      <c r="B16" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="B18" t="s">
+        <v>229</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="28.8">
+      <c r="B19" s="12"/>
+      <c r="P19" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="28.8">
+      <c r="B20" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q20" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="R20" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="43.2">
+      <c r="B21" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q21" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="R21" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="P22" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="R22" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="18">
+      <c r="B24" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="B25" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="B26" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="B27" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="G28" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="B29" t="s">
+        <v>242</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="B30" s="12"/>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="B31" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="B32" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="18">
+      <c r="A35" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="12"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E37" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E38" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="18">
+      <c r="A43" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="12"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="18">
+      <c r="A58" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="12"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="18">
+      <c r="A66" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="12"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="18">
+      <c r="A74" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="12"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="12"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="31.2">
+      <c r="A81" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" ht="18">
+      <c r="A83" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G86" s="12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="G88" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="12"/>
+      <c r="G90" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="G92" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="G93" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="31.2">
+      <c r="A97" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="12"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G100" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="18">
+      <c r="A104" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="G104" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="12"/>
+      <c r="G105" s="12"/>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="G107" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="18">
+      <c r="A108" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="31.2">
+      <c r="A109" s="12"/>
+      <c r="G109" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="18">
+      <c r="A111" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="G111" s="11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="G112" s="12"/>
+    </row>
+    <row r="113" spans="1:7" ht="18">
+      <c r="A113" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="12"/>
+      <c r="G114" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="G116" s="12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="G117" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="C119" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="18">
+      <c r="C121" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="18">
+      <c r="C123" s="11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="18">
+      <c r="C125" s="11" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="18">
+      <c r="C127" s="11" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
